--- a/samples/Инфо.xlsx
+++ b/samples/Инфо.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kostyan\Yandex.Disk\AutoAct\samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C780BC80-814F-4CC1-813C-B3D61418EC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1CFD71-F690-43E4-8820-7315F083A8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,63 +35,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
-    <t>Номер акта</t>
-  </si>
-  <si>
-    <t>Имя</t>
-  </si>
-  <si>
-    <t>СНИЛС</t>
-  </si>
-  <si>
-    <t>Должность</t>
-  </si>
-  <si>
-    <t>Отдел</t>
-  </si>
-  <si>
-    <t>Управление</t>
-  </si>
-  <si>
-    <t>Дата</t>
-  </si>
-  <si>
-    <t>Помещение</t>
-  </si>
-  <si>
-    <t>Адрес</t>
-  </si>
-  <si>
-    <t>Наименование ЭВМ</t>
-  </si>
-  <si>
-    <t>S/N ЭВМ</t>
-  </si>
-  <si>
-    <t>IP-адрес</t>
-  </si>
-  <si>
-    <t>Номер диска</t>
-  </si>
-  <si>
-    <t>ОС</t>
-  </si>
-  <si>
-    <t>ID VipNet</t>
-  </si>
-  <si>
-    <t>Номер криптосредства</t>
-  </si>
-  <si>
-    <t>Дата криптосредства</t>
-  </si>
-  <si>
-    <t>Номер стикера</t>
-  </si>
-  <si>
-    <t>Начальник</t>
-  </si>
-  <si>
     <t>Щербинина Людмила Анатольевна</t>
   </si>
   <si>
@@ -150,15 +93,72 @@
   <si>
     <t>Белослудцева Д. Н.</t>
   </si>
+  <si>
+    <t>{act_number}</t>
+  </si>
+  <si>
+    <t>{name}</t>
+  </si>
+  <si>
+    <t>{snils}</t>
+  </si>
+  <si>
+    <t>{job_title}</t>
+  </si>
+  <si>
+    <t>{department}</t>
+  </si>
+  <si>
+    <t>{control}</t>
+  </si>
+  <si>
+    <t>{date}</t>
+  </si>
+  <si>
+    <t>{room}</t>
+  </si>
+  <si>
+    <t>{adress}</t>
+  </si>
+  <si>
+    <t>{comp_name}</t>
+  </si>
+  <si>
+    <t>{serial_number}</t>
+  </si>
+  <si>
+    <t>{ip}</t>
+  </si>
+  <si>
+    <t>{disk_number}</t>
+  </si>
+  <si>
+    <t>{os}</t>
+  </si>
+  <si>
+    <t>{id_vipnet}</t>
+  </si>
+  <si>
+    <t>{crypto_number}</t>
+  </si>
+  <si>
+    <t>{crypto_date}</t>
+  </si>
+  <si>
+    <t>{sticker_number}</t>
+  </si>
+  <si>
+    <t>{boss}</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="dd\.mm\.yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,6 +197,19 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -219,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -233,7 +246,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -247,6 +260,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -526,10 +545,10 @@
   <dimension ref="A1:S2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="15.5703125" customWidth="1"/>
     <col min="3" max="4" width="10.42578125" customWidth="1"/>
-    <col min="5" max="5" width="6.85546875" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" customWidth="1"/>
     <col min="6" max="6" width="11.42578125" customWidth="1"/>
     <col min="7" max="7" width="10.85546875" customWidth="1"/>
     <col min="8" max="8" width="11.85546875" customWidth="1"/>
@@ -541,63 +560,63 @@
     <col min="19" max="19" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="1" customFormat="1" ht="45">
+    <row r="1" spans="1:19" s="1" customFormat="1" ht="30">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:19" s="2" customFormat="1" ht="30">
@@ -605,46 +624,46 @@
         <v>220126</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G2" s="5">
         <v>46044</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="N2" s="7" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="O2" s="8" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="P2" s="3">
         <v>30225</v>
@@ -656,7 +675,7 @@
         <v>9706718</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
